--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>9</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.1592078243215956</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>19</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.1775527281373836</v>
       </c>
@@ -1567,9 +1561,6 @@
       <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -1963,9 +1954,6 @@
       <c r="O8" t="n">
         <v>13</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.1214834455676835</v>
       </c>
@@ -2369,9 +2357,6 @@
       <c r="O10" t="n">
         <v>4</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -2765,9 +2750,6 @@
       <c r="O12" t="n">
         <v>25</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.2336220107070837</v>
       </c>
@@ -3171,9 +3153,6 @@
       <c r="O14" t="n">
         <v>5</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.08844879128977531</v>
       </c>
@@ -3567,9 +3546,6 @@
       <c r="O16" t="n">
         <v>19</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.1775527281373836</v>
       </c>
@@ -3973,9 +3949,6 @@
       <c r="O18" t="n">
         <v>6</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.1061385495477304</v>
       </c>
@@ -4369,9 +4342,6 @@
       <c r="O20" t="n">
         <v>22</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.2055873694222336</v>
       </c>
@@ -4775,9 +4745,6 @@
       <c r="O22" t="n">
         <v>6</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.1061385495477304</v>
       </c>
@@ -5171,9 +5138,6 @@
       <c r="O24" t="n">
         <v>23</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.214932249850517</v>
       </c>
@@ -5572,16 +5536,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5734,10 +5695,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5973,9 +5934,6 @@
       <c r="O28" t="n">
         <v>12</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.1121385651394002</v>
       </c>
@@ -6377,9 +6335,6 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
@@ -6881,7 +6836,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -6332,13 +6332,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -1166,11 +1166,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1191,14 +1186,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1206,7 +1196,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1422,7 +1412,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1430,14 +1420,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1445,7 +1430,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1962,11 +1947,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1979,7 +1959,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1987,14 +1967,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -2002,7 +1977,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2218,7 +2193,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2226,14 +2201,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT9" t="n">
@@ -2241,7 +2211,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2758,11 +2728,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2775,7 +2740,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2783,14 +2748,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT12" t="n">
@@ -2798,7 +2758,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3014,7 +2974,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -3022,14 +2982,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT13" t="n">
@@ -3037,7 +2992,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3554,11 +3509,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3571,7 +3521,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3579,14 +3529,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT16" t="n">
@@ -3594,7 +3539,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3810,7 +3755,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3818,14 +3763,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT17" t="n">
@@ -3833,7 +3773,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -4350,11 +4290,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4367,7 +4302,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4375,14 +4310,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT20" t="n">
@@ -4390,7 +4320,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4606,7 +4536,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4614,14 +4544,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT21" t="n">
@@ -4629,7 +4554,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -5146,11 +5071,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5163,7 +5083,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5171,14 +5091,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT24" t="n">
@@ -5186,7 +5101,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5402,7 +5317,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5410,14 +5325,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT25" t="n">
@@ -5425,7 +5335,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5942,11 +5852,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5959,7 +5864,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5967,14 +5872,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5982,7 +5882,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -6198,7 +6098,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -6206,14 +6106,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -6221,7 +6116,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">

--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -6553,6 +6553,399 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>penicillin-non-susceptible-resistant-pneumococcal-surveillance</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>青霉素敏感性降低或耐药肺炎球菌监测</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>penicillin-non-susceptible-resistant-pneumococcal-surveillance</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>青霉素敏感性降低或耐药肺炎球菌监测</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>PRP-infeksjon/-smittebærertilstand</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_PRP_infection_or_carriage</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>FHI MSIS penicillin-resistant pneumococcal surveillance explicitly includes infection and carriage.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6586,7 +6979,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -6669,7 +7062,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -6679,7 +7072,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -6699,7 +7092,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
